--- a/Data/POM/POM_Quizzes.xlsx
+++ b/Data/POM/POM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\POM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C99533-5093-48D9-BB15-7CC6C4F19E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98ECA8C-8519-41B2-AD87-B4B9E6A3FBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{3CF5B5CF-CFFB-4DDB-9D99-4F8875C2A1B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3CF5B5CF-CFFB-4DDB-9D99-4F8875C2A1B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="951">
   <si>
     <t>Middle level managers</t>
   </si>
@@ -2086,21 +2086,6 @@
     <t>_____ can also be used for developmental purposes by letting employees know where they stand in comparison to their peers—they can be motivated to improve performance</t>
   </si>
   <si>
-    <t>Self-Actualization</t>
-  </si>
-  <si>
-    <t>Esteem need</t>
-  </si>
-  <si>
-    <t>Safety need</t>
-  </si>
-  <si>
-    <t>Social need</t>
-  </si>
-  <si>
-    <t>According to Douglas McGregor, Maslow’s need based theory is grouped as Lower Order and Upper Order, Find which one is upper order?</t>
-  </si>
-  <si>
     <t>Paired comparison method</t>
   </si>
   <si>
@@ -2173,12 +2158,6 @@
     <t>b, d, a, c, e</t>
   </si>
   <si>
-    <t>Security needs</t>
-  </si>
-  <si>
-    <t>Rearrange Maslow’s hierarchy of needs logically</t>
-  </si>
-  <si>
     <t>Belongingness needs</t>
   </si>
   <si>
@@ -2888,6 +2867,40 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Decision Making</t>
+  </si>
+  <si>
+    <t>Hierarchy of authority, Written rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> All the given option</t>
+  </si>
+  <si>
+    <t>Rearrange Maslow’s hierarchy of needs logically: a)  Security needs b) Esteem needs c)  Psychological needs d)  Self-actualization needs e)  Social needs</t>
+  </si>
+  <si>
+    <t>b, a, d, c, e</t>
+  </si>
+  <si>
+    <t>a, d, b, c, e</t>
+  </si>
+  <si>
+    <t>According to Douglas McGregor, Maslow’s need based theory is grouped as Lower Order and Upper Order, Find which one is upper order?
+a)  Social need b) Safety need c)  Esteem need d)  Self-Actualization e) Physiological need</t>
+  </si>
+  <si>
+    <t>b, c, e</t>
+  </si>
+  <si>
+    <t>c, d, e</t>
+  </si>
+  <si>
+    <t>a, b, e</t>
+  </si>
+  <si>
+    <t>a, d, e</t>
   </si>
 </sst>
 </file>
@@ -3011,7 +3024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -3025,6 +3038,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3414,7 +3430,7 @@
         <v>102</v>
       </c>
       <c r="G2" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3435,7 +3451,7 @@
       </c>
       <c r="F3" s="8"/>
       <c r="G3" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3458,7 +3474,7 @@
         <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3481,7 +3497,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3504,7 +3520,7 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3527,7 +3543,7 @@
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3550,7 +3566,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3573,7 +3589,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3596,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3616,10 +3632,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>19</v>
+        <v>940</v>
       </c>
       <c r="G11" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3642,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3665,7 +3681,7 @@
         <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3688,7 +3704,7 @@
         <v>87</v>
       </c>
       <c r="G14" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3711,7 +3727,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3734,7 +3750,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3761,19 @@
         <v>75</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G17" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3780,7 +3796,7 @@
         <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3803,7 +3819,7 @@
         <v>59</v>
       </c>
       <c r="G19" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3826,7 +3842,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3849,7 +3865,7 @@
         <v>42</v>
       </c>
       <c r="G21" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -3898,22 +3914,22 @@
         <v>105</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>212</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,22 +3937,22 @@
         <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,22 +3960,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3967,22 +3983,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3990,22 +4006,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,22 +4029,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,22 +4052,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>201</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,22 +4075,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4082,22 +4098,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,22 +4121,22 @@
         <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,22 +4144,22 @@
         <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>650</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,22 +4167,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,22 +4190,22 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,22 +4213,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>617</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,22 +4236,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,22 +4259,22 @@
         <v>76</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,22 +4282,22 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,22 +4305,22 @@
         <v>64</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4312,22 +4328,22 @@
         <v>58</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>90</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>283</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,22 +4351,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -4400,22 +4416,22 @@
         <v>105</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4423,22 +4439,22 @@
         <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>319</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4446,22 +4462,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>201</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4469,22 +4485,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>201</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4492,22 +4508,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4515,22 +4531,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>201</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4538,22 +4554,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4561,22 +4577,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4584,22 +4600,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4607,22 +4623,22 @@
         <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4630,22 +4646,22 @@
         <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4653,7 +4669,7 @@
         <v>95</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>19</v>
@@ -4668,7 +4684,7 @@
         <v>385</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4676,22 +4692,22 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4699,22 +4715,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4722,22 +4738,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4745,22 +4761,22 @@
         <v>76</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4768,22 +4784,22 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>74</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4791,22 +4807,22 @@
         <v>64</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>201</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4814,22 +4830,22 @@
         <v>58</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4837,22 +4853,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -4903,22 +4919,22 @@
         <v>105</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>939</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4926,22 +4942,22 @@
         <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4949,22 +4965,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4972,22 +4988,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4995,22 +5011,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>335</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5018,22 +5034,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5041,22 +5057,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>898</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>905</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5064,22 +5080,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5087,22 +5103,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5110,22 +5126,22 @@
         <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>926</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>937</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>936</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>933</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5133,22 +5149,22 @@
         <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5156,22 +5172,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5179,7 +5195,7 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>18</v>
@@ -5194,7 +5210,7 @@
         <v>385</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5202,22 +5218,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5225,22 +5241,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5248,22 +5264,22 @@
         <v>76</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5271,22 +5287,22 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5294,7 +5310,7 @@
         <v>64</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>18</v>
@@ -5309,7 +5325,7 @@
         <v>19</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5317,22 +5333,22 @@
         <v>58</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5340,22 +5356,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -5370,8 +5386,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="37.42578125" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5418,7 +5434,7 @@
         <v>190</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5441,7 +5457,7 @@
         <v>148</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5464,7 +5480,7 @@
         <v>138</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5487,7 +5503,7 @@
         <v>134</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5510,7 +5526,7 @@
         <v>131</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5531,7 +5547,7 @@
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5554,7 +5570,7 @@
         <v>122</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5577,7 +5593,7 @@
         <v>117</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,7 +5616,7 @@
         <v>112</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5623,7 +5639,7 @@
         <v>185</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,7 +5662,7 @@
         <v>181</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5657,7 +5673,7 @@
         <v>180</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>153</v>
+        <v>941</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>155</v>
@@ -5666,10 +5682,10 @@
         <v>154</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>156</v>
+        <v>942</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5690,7 +5706,7 @@
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5711,7 +5727,7 @@
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5734,7 +5750,7 @@
         <v>167</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5757,7 +5773,7 @@
         <v>162</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5780,7 +5796,7 @@
         <v>132</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5803,7 +5819,7 @@
         <v>53</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5826,7 +5842,7 @@
         <v>153</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5849,7 +5865,7 @@
         <v>143</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -5865,10 +5881,7 @@
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5915,7 +5928,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5926,19 +5939,19 @@
         <v>236</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>233</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5961,7 +5974,7 @@
         <v>224</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5984,7 +5997,7 @@
         <v>219</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6007,7 +6020,7 @@
         <v>201</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6030,7 +6043,7 @@
         <v>210</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6053,7 +6066,7 @@
         <v>205</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6076,7 +6089,7 @@
         <v>200</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6099,7 +6112,7 @@
         <v>195</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6122,7 +6135,7 @@
         <v>206</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6145,7 +6158,7 @@
         <v>271</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6168,7 +6181,7 @@
         <v>268</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6191,7 +6204,7 @@
         <v>263</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6214,7 +6227,7 @@
         <v>259</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6237,7 +6250,7 @@
         <v>201</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6260,7 +6273,7 @@
         <v>250</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6283,7 +6296,7 @@
         <v>245</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6306,7 +6319,7 @@
         <v>195</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6329,7 +6342,7 @@
         <v>237</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6352,7 +6365,7 @@
         <v>229</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -6368,10 +6381,7 @@
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6417,7 +6427,7 @@
         <v>352</v>
       </c>
       <c r="G2" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6440,7 +6450,7 @@
         <v>250</v>
       </c>
       <c r="G3" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6463,7 +6473,7 @@
         <v>307</v>
       </c>
       <c r="G4" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6486,7 +6496,7 @@
         <v>303</v>
       </c>
       <c r="G5" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6509,7 +6519,7 @@
         <v>298</v>
       </c>
       <c r="G6" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6532,7 +6542,7 @@
         <v>294</v>
       </c>
       <c r="G7" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6555,7 +6565,7 @@
         <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6578,7 +6588,7 @@
         <v>285</v>
       </c>
       <c r="G9" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6601,7 +6611,7 @@
         <v>281</v>
       </c>
       <c r="G10" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6624,7 +6634,7 @@
         <v>201</v>
       </c>
       <c r="G11" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6647,7 +6657,7 @@
         <v>304</v>
       </c>
       <c r="G12" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6670,7 +6680,7 @@
         <v>326</v>
       </c>
       <c r="G13" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6693,7 +6703,7 @@
         <v>342</v>
       </c>
       <c r="G14" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6716,7 +6726,7 @@
         <v>337</v>
       </c>
       <c r="G15" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6739,7 +6749,7 @@
         <v>333</v>
       </c>
       <c r="G16" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6762,7 +6772,7 @@
         <v>328</v>
       </c>
       <c r="G17" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6785,7 +6795,7 @@
         <v>323</v>
       </c>
       <c r="G18" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6808,7 +6818,7 @@
         <v>295</v>
       </c>
       <c r="G19" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6831,7 +6841,7 @@
         <v>192</v>
       </c>
       <c r="G20" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6854,7 +6864,7 @@
         <v>311</v>
       </c>
       <c r="G21" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -6920,7 +6930,7 @@
         <v>395</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6943,7 +6953,7 @@
         <v>385</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6966,7 +6976,7 @@
         <v>379</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6989,7 +6999,7 @@
         <v>374</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7012,7 +7022,7 @@
         <v>185</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7035,7 +7045,7 @@
         <v>368</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7058,7 +7068,7 @@
         <v>363</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7081,7 +7091,7 @@
         <v>359</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7104,7 +7114,7 @@
         <v>354</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7127,7 +7137,7 @@
         <v>417</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7150,7 +7160,7 @@
         <v>373</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7173,7 +7183,7 @@
         <v>201</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7196,7 +7206,7 @@
         <v>405</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7219,7 +7229,7 @@
         <v>373</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7242,7 +7252,7 @@
         <v>398</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7265,7 +7275,7 @@
         <v>394</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7288,7 +7298,7 @@
         <v>389</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7311,7 +7321,7 @@
         <v>19</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7334,7 +7344,7 @@
         <v>373</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7357,7 +7367,7 @@
         <v>185</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -7421,7 +7431,7 @@
         <v>485</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7444,7 +7454,7 @@
         <v>446</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7467,7 +7477,7 @@
         <v>446</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7490,7 +7500,7 @@
         <v>441</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7513,7 +7523,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7536,7 +7546,7 @@
         <v>394</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7559,7 +7569,7 @@
         <v>430</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7582,7 +7592,7 @@
         <v>426</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7605,7 +7615,7 @@
         <v>410</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7628,7 +7638,7 @@
         <v>409</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7651,7 +7661,7 @@
         <v>201</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7674,7 +7684,7 @@
         <v>476</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7697,7 +7707,7 @@
         <v>475</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7720,7 +7730,7 @@
         <v>468</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7743,7 +7753,7 @@
         <v>465</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7766,7 +7776,7 @@
         <v>193</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7789,7 +7799,7 @@
         <v>465</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7812,7 +7822,7 @@
         <v>461</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7835,7 +7845,7 @@
         <v>458</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7858,7 +7868,7 @@
         <v>437</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -7922,7 +7932,7 @@
         <v>564</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7945,7 +7955,7 @@
         <v>519</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7968,7 +7978,7 @@
         <v>512</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7991,7 +8001,7 @@
         <v>508</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8014,7 +8024,7 @@
         <v>504</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8037,7 +8047,7 @@
         <v>499</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8060,7 +8070,7 @@
         <v>436</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8083,7 +8093,7 @@
         <v>492</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8106,7 +8116,7 @@
         <v>201</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8129,7 +8139,7 @@
         <v>559</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8152,7 +8162,7 @@
         <v>512</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8175,7 +8185,7 @@
         <v>553</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8198,7 +8208,7 @@
         <v>549</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8221,7 +8231,7 @@
         <v>544</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8244,7 +8254,7 @@
         <v>539</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8267,7 +8277,7 @@
         <v>535</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8290,7 +8300,7 @@
         <v>530</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8313,7 +8323,7 @@
         <v>525</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8336,7 +8346,7 @@
         <v>515</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8359,7 +8369,7 @@
         <v>514</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -8421,7 +8431,7 @@
         <v>643</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8444,7 +8454,7 @@
         <v>470</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8467,7 +8477,7 @@
         <v>470</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8490,7 +8500,7 @@
         <v>593</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8513,7 +8523,7 @@
         <v>588</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8536,7 +8546,7 @@
         <v>583</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8559,7 +8569,7 @@
         <v>578</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8582,7 +8592,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8605,7 +8615,7 @@
         <v>569</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8628,7 +8638,7 @@
         <v>639</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8651,7 +8661,7 @@
         <v>195</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8674,7 +8684,7 @@
         <v>74</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8697,7 +8707,7 @@
         <v>201</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8720,7 +8730,7 @@
         <v>623</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8743,7 +8753,7 @@
         <v>201</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8766,7 +8776,7 @@
         <v>614</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8789,7 +8799,7 @@
         <v>201</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8812,7 +8822,7 @@
         <v>608</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8835,7 +8845,7 @@
         <v>292</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8858,7 +8868,7 @@
         <v>599</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -8917,22 +8927,22 @@
         <v>105</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>427</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -8944,22 +8954,22 @@
         <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -8986,7 +8996,7 @@
         <v>674</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -9013,7 +9023,7 @@
         <v>670</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -9040,7 +9050,7 @@
         <v>665</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -9067,7 +9077,7 @@
         <v>660</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -9094,7 +9104,7 @@
         <v>655</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -9121,7 +9131,7 @@
         <v>652</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -9148,7 +9158,7 @@
         <v>647</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -9160,10 +9170,10 @@
         <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>650</v>
@@ -9175,7 +9185,7 @@
         <v>426</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -9187,22 +9197,22 @@
         <v>99</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -9214,22 +9224,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -9241,13 +9251,13 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -9256,7 +9266,7 @@
         <v>650</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -9268,22 +9278,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
@@ -9295,22 +9305,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -9322,22 +9332,22 @@
         <v>76</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>709</v>
+        <v>943</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>705</v>
+        <v>700</v>
+      </c>
+      <c r="E17" t="s">
+        <v>944</v>
+      </c>
+      <c r="F17" t="s">
+        <v>945</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -9349,22 +9359,22 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -9376,22 +9386,22 @@
         <v>64</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -9403,49 +9413,49 @@
         <v>58</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>679</v>
+      <c r="B21" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="C21" t="s">
+        <v>947</v>
+      </c>
+      <c r="D21" t="s">
+        <v>948</v>
+      </c>
+      <c r="E21" t="s">
+        <v>949</v>
+      </c>
+      <c r="F21" t="s">
+        <v>950</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
